--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -2769,7 +2769,7 @@
         <v>136687800</v>
       </c>
       <c r="B21" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>136689310</v>
       </c>
       <c r="B22" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136689322</v>
       </c>
       <c r="B23" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>136689361</v>
       </c>
       <c r="B24" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3237,7 +3237,7 @@
         <v>136689307</v>
       </c>
       <c r="B25" t="n">
-        <v>89316</v>
+        <v>89318</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>136689311</v>
       </c>
       <c r="B26" t="n">
-        <v>89316</v>
+        <v>89318</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>136689313</v>
       </c>
       <c r="B27" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>136689314</v>
       </c>
       <c r="B28" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>136689356</v>
       </c>
       <c r="B29" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3805,7 +3805,7 @@
         <v>136689357</v>
       </c>
       <c r="B30" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3921,7 +3921,7 @@
         <v>136699215</v>
       </c>
       <c r="B31" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>136699216</v>
       </c>
       <c r="B32" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>136699217</v>
       </c>
       <c r="B33" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>136689324</v>
       </c>
       <c r="B174" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>136689294</v>
       </c>
       <c r="B175" t="n">
-        <v>79498</v>
+        <v>79500</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>136689297</v>
       </c>
       <c r="B176" t="n">
-        <v>79498</v>
+        <v>79500</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>136699227</v>
       </c>
       <c r="B183" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>136687801</v>
       </c>
       <c r="B200" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
         <v>136689298</v>
       </c>
       <c r="B215" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>136689299</v>
       </c>
       <c r="B216" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>136689300</v>
       </c>
       <c r="B217" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>136689301</v>
       </c>
       <c r="B218" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>136689305</v>
       </c>
       <c r="B219" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>136689312</v>
       </c>
       <c r="B222" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>136689306</v>
       </c>
       <c r="B224" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -27034,7 +27034,7 @@
         <v>136689293</v>
       </c>
       <c r="B234" t="n">
-        <v>58627</v>
+        <v>58629</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>136689308</v>
       </c>
       <c r="B258" t="n">
-        <v>111325</v>
+        <v>111330</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>136689315</v>
       </c>
       <c r="B260" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>136689318</v>
       </c>
       <c r="B261" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>136689358</v>
       </c>
       <c r="B263" t="n">
-        <v>104869</v>
+        <v>104874</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -30430,7 +30430,7 @@
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -3237,7 +3237,7 @@
         <v>136689307</v>
       </c>
       <c r="B25" t="n">
-        <v>89318</v>
+        <v>89320</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>136689311</v>
       </c>
       <c r="B26" t="n">
-        <v>89318</v>
+        <v>89320</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>136689313</v>
       </c>
       <c r="B27" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>136689314</v>
       </c>
       <c r="B28" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>136689356</v>
       </c>
       <c r="B29" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>136689357</v>
       </c>
       <c r="B30" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>136699215</v>
       </c>
       <c r="B31" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>136699216</v>
       </c>
       <c r="B32" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>136699217</v>
       </c>
       <c r="B33" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>136689308</v>
       </c>
       <c r="B258" t="n">
-        <v>111330</v>
+        <v>111332</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>136689315</v>
       </c>
       <c r="B260" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>136689318</v>
       </c>
       <c r="B261" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>136689358</v>
       </c>
       <c r="B263" t="n">
-        <v>104874</v>
+        <v>104876</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -30430,7 +30430,7 @@
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -2769,7 +2769,7 @@
         <v>136687800</v>
       </c>
       <c r="B21" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>136689310</v>
       </c>
       <c r="B22" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136689322</v>
       </c>
       <c r="B23" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>136689361</v>
       </c>
       <c r="B24" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>136689307</v>
       </c>
       <c r="B25" t="n">
-        <v>89320</v>
+        <v>89322</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>136689311</v>
       </c>
       <c r="B26" t="n">
-        <v>89320</v>
+        <v>89322</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>136689313</v>
       </c>
       <c r="B27" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>136689314</v>
       </c>
       <c r="B28" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>136689356</v>
       </c>
       <c r="B29" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>136689357</v>
       </c>
       <c r="B30" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>136699215</v>
       </c>
       <c r="B31" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4037,7 +4037,7 @@
         <v>136699216</v>
       </c>
       <c r="B32" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4153,7 +4153,7 @@
         <v>136699217</v>
       </c>
       <c r="B33" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -20094,7 +20094,7 @@
         <v>136689324</v>
       </c>
       <c r="B174" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>136689294</v>
       </c>
       <c r="B175" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>136689297</v>
       </c>
       <c r="B176" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>136699227</v>
       </c>
       <c r="B183" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -23005,7 +23005,7 @@
         <v>136687801</v>
       </c>
       <c r="B200" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>136689308</v>
       </c>
       <c r="B258" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>136689315</v>
       </c>
       <c r="B260" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>136689318</v>
       </c>
       <c r="B261" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>136689358</v>
       </c>
       <c r="B263" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -2769,7 +2769,7 @@
         <v>136687800</v>
       </c>
       <c r="B21" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>136689310</v>
       </c>
       <c r="B22" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136689322</v>
       </c>
       <c r="B23" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>136689361</v>
       </c>
       <c r="B24" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>136689307</v>
       </c>
       <c r="B25" t="n">
-        <v>89322</v>
+        <v>89324</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>136689311</v>
       </c>
       <c r="B26" t="n">
-        <v>89322</v>
+        <v>89324</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>136689313</v>
       </c>
       <c r="B27" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>136689314</v>
       </c>
       <c r="B28" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>136689356</v>
       </c>
       <c r="B29" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>136689357</v>
       </c>
       <c r="B30" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>136699215</v>
       </c>
       <c r="B31" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4037,7 +4037,7 @@
         <v>136699216</v>
       </c>
       <c r="B32" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4153,7 +4153,7 @@
         <v>136699217</v>
       </c>
       <c r="B33" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -20094,7 +20094,7 @@
         <v>136689324</v>
       </c>
       <c r="B174" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>136689294</v>
       </c>
       <c r="B175" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>136689297</v>
       </c>
       <c r="B176" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>136699227</v>
       </c>
       <c r="B183" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -23005,7 +23005,7 @@
         <v>136687801</v>
       </c>
       <c r="B200" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>136689308</v>
       </c>
       <c r="B258" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>136689315</v>
       </c>
       <c r="B260" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>136689318</v>
       </c>
       <c r="B261" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>136689358</v>
       </c>
       <c r="B263" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -2769,7 +2769,7 @@
         <v>136687800</v>
       </c>
       <c r="B21" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>136689310</v>
       </c>
       <c r="B22" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136689322</v>
       </c>
       <c r="B23" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>136689361</v>
       </c>
       <c r="B24" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>136689307</v>
       </c>
       <c r="B25" t="n">
-        <v>89324</v>
+        <v>89325</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>136689311</v>
       </c>
       <c r="B26" t="n">
-        <v>89324</v>
+        <v>89325</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>136689313</v>
       </c>
       <c r="B27" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>136689314</v>
       </c>
       <c r="B28" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>136689356</v>
       </c>
       <c r="B29" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>136689357</v>
       </c>
       <c r="B30" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>136699215</v>
       </c>
       <c r="B31" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>136699216</v>
       </c>
       <c r="B32" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>136699217</v>
       </c>
       <c r="B33" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>136689324</v>
       </c>
       <c r="B174" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>136689294</v>
       </c>
       <c r="B175" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>136689297</v>
       </c>
       <c r="B176" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>136699227</v>
       </c>
       <c r="B183" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>136687801</v>
       </c>
       <c r="B200" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>136689308</v>
       </c>
       <c r="B258" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>136689315</v>
       </c>
       <c r="B260" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>136689318</v>
       </c>
       <c r="B261" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>136689358</v>
       </c>
       <c r="B263" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -3237,7 +3237,7 @@
         <v>136689307</v>
       </c>
       <c r="B25" t="n">
-        <v>89325</v>
+        <v>89331</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>136689311</v>
       </c>
       <c r="B26" t="n">
-        <v>89325</v>
+        <v>89331</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>136689313</v>
       </c>
       <c r="B27" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>136689314</v>
       </c>
       <c r="B28" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>136689356</v>
       </c>
       <c r="B29" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>136689357</v>
       </c>
       <c r="B30" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>136699215</v>
       </c>
       <c r="B31" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>136699216</v>
       </c>
       <c r="B32" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>136699217</v>
       </c>
       <c r="B33" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>136689308</v>
       </c>
       <c r="B258" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>136689315</v>
       </c>
       <c r="B260" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>136689318</v>
       </c>
       <c r="B261" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>136689358</v>
       </c>
       <c r="B263" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -2769,7 +2769,7 @@
         <v>136687800</v>
       </c>
       <c r="B21" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>136689310</v>
       </c>
       <c r="B22" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136689322</v>
       </c>
       <c r="B23" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>136689361</v>
       </c>
       <c r="B24" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>136689307</v>
       </c>
       <c r="B25" t="n">
-        <v>89331</v>
+        <v>89335</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>136689311</v>
       </c>
       <c r="B26" t="n">
-        <v>89331</v>
+        <v>89335</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>136689313</v>
       </c>
       <c r="B27" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>136689314</v>
       </c>
       <c r="B28" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>136689356</v>
       </c>
       <c r="B29" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>136689357</v>
       </c>
       <c r="B30" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>136699215</v>
       </c>
       <c r="B31" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>136699216</v>
       </c>
       <c r="B32" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>136699217</v>
       </c>
       <c r="B33" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>136689324</v>
       </c>
       <c r="B174" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>136689294</v>
       </c>
       <c r="B175" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>136689297</v>
       </c>
       <c r="B176" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>136699227</v>
       </c>
       <c r="B183" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>136687801</v>
       </c>
       <c r="B200" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>136689308</v>
       </c>
       <c r="B258" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>136689315</v>
       </c>
       <c r="B260" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>136689318</v>
       </c>
       <c r="B261" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>136689358</v>
       </c>
       <c r="B263" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -29783,7 +29783,7 @@
         <v>136689308</v>
       </c>
       <c r="B258" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>136689315</v>
       </c>
       <c r="B260" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>136689318</v>
       </c>
       <c r="B261" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>136689358</v>
       </c>
       <c r="B263" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -2769,7 +2769,7 @@
         <v>136687800</v>
       </c>
       <c r="B21" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>136689310</v>
       </c>
       <c r="B22" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136689322</v>
       </c>
       <c r="B23" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>136689361</v>
       </c>
       <c r="B24" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>136689307</v>
       </c>
       <c r="B25" t="n">
-        <v>89335</v>
+        <v>89337</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>136689311</v>
       </c>
       <c r="B26" t="n">
-        <v>89335</v>
+        <v>89337</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>136689313</v>
       </c>
       <c r="B27" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>136689314</v>
       </c>
       <c r="B28" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>136689356</v>
       </c>
       <c r="B29" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>136689357</v>
       </c>
       <c r="B30" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>136699215</v>
       </c>
       <c r="B31" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>136699216</v>
       </c>
       <c r="B32" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>136699217</v>
       </c>
       <c r="B33" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>136689324</v>
       </c>
       <c r="B174" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>136689294</v>
       </c>
       <c r="B175" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>136689297</v>
       </c>
       <c r="B176" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>136699227</v>
       </c>
       <c r="B183" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>136687801</v>
       </c>
       <c r="B200" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>136689308</v>
       </c>
       <c r="B258" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>136689315</v>
       </c>
       <c r="B260" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>136689318</v>
       </c>
       <c r="B261" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>136689358</v>
       </c>
       <c r="B263" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -2769,7 +2769,7 @@
         <v>136687800</v>
       </c>
       <c r="B21" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>136689310</v>
       </c>
       <c r="B22" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136689322</v>
       </c>
       <c r="B23" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>136689361</v>
       </c>
       <c r="B24" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>136689307</v>
       </c>
       <c r="B25" t="n">
-        <v>89337</v>
+        <v>89350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>136689311</v>
       </c>
       <c r="B26" t="n">
-        <v>89337</v>
+        <v>89350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>136689313</v>
       </c>
       <c r="B27" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>136689314</v>
       </c>
       <c r="B28" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>136689356</v>
       </c>
       <c r="B29" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>136689357</v>
       </c>
       <c r="B30" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>136699215</v>
       </c>
       <c r="B31" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>136699216</v>
       </c>
       <c r="B32" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>136699217</v>
       </c>
       <c r="B33" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>136689324</v>
       </c>
       <c r="B174" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>136689294</v>
       </c>
       <c r="B175" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>136689297</v>
       </c>
       <c r="B176" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>136699227</v>
       </c>
       <c r="B183" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>136687801</v>
       </c>
       <c r="B200" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
         <v>136689298</v>
       </c>
       <c r="B215" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>136689299</v>
       </c>
       <c r="B216" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>136689300</v>
       </c>
       <c r="B217" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>136689301</v>
       </c>
       <c r="B218" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>136689305</v>
       </c>
       <c r="B219" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>136689312</v>
       </c>
       <c r="B222" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>136689306</v>
       </c>
       <c r="B224" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -27034,7 +27034,7 @@
         <v>136689293</v>
       </c>
       <c r="B234" t="n">
-        <v>58629</v>
+        <v>58642</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>136689308</v>
       </c>
       <c r="B258" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>136689315</v>
       </c>
       <c r="B260" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>136689318</v>
       </c>
       <c r="B261" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>136689358</v>
       </c>
       <c r="B263" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -2769,7 +2769,7 @@
         <v>136687800</v>
       </c>
       <c r="B21" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>136689310</v>
       </c>
       <c r="B22" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136689322</v>
       </c>
       <c r="B23" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>136689361</v>
       </c>
       <c r="B24" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>136689307</v>
       </c>
       <c r="B25" t="n">
-        <v>89350</v>
+        <v>89352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>136689311</v>
       </c>
       <c r="B26" t="n">
-        <v>89350</v>
+        <v>89352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>136689313</v>
       </c>
       <c r="B27" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>136689314</v>
       </c>
       <c r="B28" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>136689356</v>
       </c>
       <c r="B29" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>136689357</v>
       </c>
       <c r="B30" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>136699215</v>
       </c>
       <c r="B31" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>136699216</v>
       </c>
       <c r="B32" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>136699217</v>
       </c>
       <c r="B33" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>136689324</v>
       </c>
       <c r="B174" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>136689294</v>
       </c>
       <c r="B175" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>136689297</v>
       </c>
       <c r="B176" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>136699227</v>
       </c>
       <c r="B183" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>136687801</v>
       </c>
       <c r="B200" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
         <v>136689298</v>
       </c>
       <c r="B215" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>136689299</v>
       </c>
       <c r="B216" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>136689300</v>
       </c>
       <c r="B217" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>136689301</v>
       </c>
       <c r="B218" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>136689305</v>
       </c>
       <c r="B219" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>136689312</v>
       </c>
       <c r="B222" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>136689306</v>
       </c>
       <c r="B224" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -27034,7 +27034,7 @@
         <v>136689293</v>
       </c>
       <c r="B234" t="n">
-        <v>58642</v>
+        <v>58644</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>136689302</v>
       </c>
       <c r="B256" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>136689325</v>
       </c>
       <c r="B257" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>136689308</v>
       </c>
       <c r="B258" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>136689315</v>
       </c>
       <c r="B260" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>136689318</v>
       </c>
       <c r="B261" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>136689358</v>
       </c>
       <c r="B263" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -24824,11 +24824,7 @@
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
@@ -24941,11 +24937,7 @@
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
@@ -25058,11 +25050,7 @@
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
@@ -25175,11 +25163,7 @@
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
@@ -25292,11 +25276,7 @@
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
@@ -25641,11 +25621,7 @@
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
@@ -25883,11 +25859,7 @@
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
@@ -27064,11 +27036,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
@@ -29575,11 +29543,7 @@
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
@@ -29692,11 +29656,7 @@
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -3237,7 +3237,7 @@
         <v>136689307</v>
       </c>
       <c r="B25" t="n">
-        <v>89352</v>
+        <v>89355</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>136689311</v>
       </c>
       <c r="B26" t="n">
-        <v>89352</v>
+        <v>89355</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>136689313</v>
       </c>
       <c r="B27" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>136689314</v>
       </c>
       <c r="B28" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>136689356</v>
       </c>
       <c r="B29" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>136689357</v>
       </c>
       <c r="B30" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>136699215</v>
       </c>
       <c r="B31" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>136699216</v>
       </c>
       <c r="B32" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>136699217</v>
       </c>
       <c r="B33" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>136699227</v>
       </c>
       <c r="B183" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>136689308</v>
       </c>
       <c r="B258" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>136689315</v>
       </c>
       <c r="B260" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>136689318</v>
       </c>
       <c r="B261" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>136689358</v>
       </c>
       <c r="B263" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -3921,7 +3921,7 @@
         <v>136699215</v>
       </c>
       <c r="B31" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>136699216</v>
       </c>
       <c r="B32" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>136699217</v>
       </c>
       <c r="B33" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>136699227</v>
       </c>
       <c r="B183" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
